--- a/artfynd/A 3427-2024 artfynd.xlsx
+++ b/artfynd/A 3427-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3427-2024 artfynd.xlsx
+++ b/artfynd/A 3427-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1897,6 +1897,131 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114984088</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5161</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Röremyr, Boh</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>320629</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6462363</v>
+      </c>
+      <c r="S14" t="n">
+        <v>29</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Forshälla</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Lundström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Lundström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3427-2024 artfynd.xlsx
+++ b/artfynd/A 3427-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114630840</v>
+        <v>114630833</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>320614</v>
+        <v>320673</v>
       </c>
       <c r="R2" t="n">
-        <v>6462220</v>
+        <v>6462262</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114630825</v>
+        <v>114630834</v>
       </c>
       <c r="B3" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>320610</v>
+        <v>320662</v>
       </c>
       <c r="R3" t="n">
-        <v>6462210</v>
+        <v>6462271</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114630833</v>
+        <v>114630842</v>
       </c>
       <c r="B4" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>2606</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>320673</v>
+        <v>320688</v>
       </c>
       <c r="R4" t="n">
-        <v>6462262</v>
+        <v>6462132</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114630838</v>
+        <v>114630825</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>320657</v>
+        <v>320610</v>
       </c>
       <c r="R5" t="n">
-        <v>6462375</v>
+        <v>6462210</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114630834</v>
+        <v>114630826</v>
       </c>
       <c r="B6" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>320662</v>
+        <v>320607</v>
       </c>
       <c r="R6" t="n">
-        <v>6462271</v>
+        <v>6462331</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,12 +1163,7 @@
         <v>114630828</v>
       </c>
       <c r="B7" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114630839</v>
+        <v>114630829</v>
       </c>
       <c r="B8" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>320698</v>
+        <v>320662</v>
       </c>
       <c r="R8" t="n">
-        <v>6462299</v>
+        <v>6462266</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114630842</v>
+        <v>114630830</v>
       </c>
       <c r="B9" t="n">
-        <v>96283</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1432,7 +1392,7 @@
         <v>320688</v>
       </c>
       <c r="R9" t="n">
-        <v>6462132</v>
+        <v>6462135</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,16 +1454,11 @@
         <v>114630835</v>
       </c>
       <c r="B10" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1593,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114630829</v>
+        <v>114630837</v>
       </c>
       <c r="B11" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>320662</v>
+        <v>320667</v>
       </c>
       <c r="R11" t="n">
-        <v>6462266</v>
+        <v>6462378</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,19 +1645,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114630837</v>
+        <v>114630838</v>
       </c>
       <c r="B12" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>320667</v>
+        <v>320657</v>
       </c>
       <c r="R12" t="n">
-        <v>6462378</v>
+        <v>6462375</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114630830</v>
+        <v>114630839</v>
       </c>
       <c r="B13" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>320688</v>
+        <v>320698</v>
       </c>
       <c r="R13" t="n">
-        <v>6462135</v>
+        <v>6462299</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,12 +1842,7 @@
         <v>114984088</v>
       </c>
       <c r="B14" t="n">
-        <v>5164</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5178</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2021,6 +1956,103 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>114630840</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Röremyr, Boh</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>320614</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6462220</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Forshälla</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-02-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-02-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3427-2024 artfynd.xlsx
+++ b/artfynd/A 3427-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114630833</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114630834</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114630842</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114630825</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114630826</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114630828</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114630829</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114630830</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114630835</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114630837</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114630838</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114630839</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1956,6 +2021,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114984088</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2053,8 +2123,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114630840</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>